--- a/ketahanan pangan 2025.xlsx
+++ b/ketahanan pangan 2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\Ketahanan Pangan 2025\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A0B91A1-997E-426C-A70D-0C928DB87C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC25AE8-2DA8-44C4-BCBC-38569FC9D50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{AB567868-D36C-450B-A89E-C6C3310C1728}"/>
   </bookViews>
@@ -189,6 +189,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.000"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -327,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -350,9 +353,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -362,13 +362,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -707,6 +713,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{569276E8-7A3F-4E47-80C9-E0C2CBDD0C6A}">
   <dimension ref="A1:Y1000"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.58203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="140.5" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A1" s="1" t="s">
@@ -755,35 +765,35 @@
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
     </row>
-    <row r="2" spans="1:25" ht="40.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="2" spans="1:25" ht="21" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8">
-        <v>69999834</v>
-      </c>
-      <c r="C2" s="9">
+      <c r="B2" s="1">
+        <v>69.999834000000007</v>
+      </c>
+      <c r="C2" s="3">
         <v>1615200.08</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="4">
         <v>46744.81</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="15">
         <v>257502.43</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="4">
         <v>13443</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="4">
         <v>82.21</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="3">
         <v>92.06</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="13">
         <v>9.7200000000000006</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="14">
         <v>0.37</v>
       </c>
       <c r="K2" s="5"/>
@@ -806,31 +816,31 @@
       <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="8">
-        <v>714663313</v>
-      </c>
-      <c r="C3" s="9">
+      <c r="B3" s="7">
+        <v>71.466331299999993</v>
+      </c>
+      <c r="C3" s="8">
         <v>2752655.35</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>1279168.92</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <v>1236193.57</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <v>13920.5</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>87.47</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <v>93.24</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="9">
         <v>10.1</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="11">
         <v>0.5</v>
       </c>
       <c r="K3" s="5"/>
@@ -853,31 +863,31 @@
       <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="8">
-        <v>77723828</v>
-      </c>
-      <c r="C4" s="9">
+      <c r="B4" s="7">
+        <v>77.723827999999997</v>
+      </c>
+      <c r="C4" s="8">
         <v>1382696.68</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <v>550409.65</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <v>352189.4</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <v>15442</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>74.59</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="8">
         <v>87.26</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="10">
         <v>11.36</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="10">
         <v>1.38</v>
       </c>
       <c r="K4" s="5"/>
@@ -896,35 +906,35 @@
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
     </row>
-    <row r="5" spans="1:25" ht="40.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="5" spans="1:25" ht="21" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="8">
-        <v>704190035</v>
-      </c>
-      <c r="C5" s="9">
+      <c r="B5" s="7">
+        <v>70.419003500000002</v>
+      </c>
+      <c r="C5" s="8">
         <v>232071.27</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>4309.71</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="9">
         <v>1201383.76</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <v>14146.5</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <v>91.21</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>92.17</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="10">
         <v>9.98</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="10">
         <v>0.13</v>
       </c>
       <c r="K5" s="6"/>
@@ -947,31 +957,31 @@
       <c r="A6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="8">
-        <v>761605704</v>
-      </c>
-      <c r="C6" s="9">
+      <c r="B6" s="7">
+        <v>76.160570399999997</v>
+      </c>
+      <c r="C6" s="8">
         <v>367791</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>26737.57</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <v>349662.6</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>13101</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <v>85.88</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <v>82.46</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="10">
         <v>7.55</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="10">
         <v>0.39</v>
       </c>
       <c r="K6" s="6"/>
@@ -994,31 +1004,31 @@
       <c r="A7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="8">
-        <v>793096701</v>
-      </c>
-      <c r="C7" s="9">
+      <c r="B7" s="7">
+        <v>79.309670100000005</v>
+      </c>
+      <c r="C7" s="8">
         <v>3627022.14</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>401175.25</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <v>720205.22</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <v>12192.5</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <v>85.5</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <v>86.82</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="10">
         <v>8.4499999999999993</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="10">
         <v>1.08</v>
       </c>
       <c r="K7" s="6"/>
@@ -1041,31 +1051,31 @@
       <c r="A8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="8">
-        <v>698867218</v>
-      </c>
-      <c r="C8" s="9">
+      <c r="B8" s="7">
+        <v>69.886721800000004</v>
+      </c>
+      <c r="C8" s="8">
         <v>266567.39</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>66703.87</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="9">
         <v>111829.42</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="9">
         <v>13309</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <v>85.75</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <v>70.47</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="10">
         <v>11.97</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="10">
         <v>1.87</v>
       </c>
       <c r="K8" s="6"/>
@@ -1088,31 +1098,31 @@
       <c r="A9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="8">
-        <v>730594723</v>
-      </c>
-      <c r="C9" s="9">
+      <c r="B9" s="7">
+        <v>73.059472299999996</v>
+      </c>
+      <c r="C9" s="8">
         <v>3252627.27</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>1259482.21</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="9">
         <v>523846.54</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="9">
         <v>12951.5</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <v>87.29</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>85.13</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="10">
         <v>6.75</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="10">
         <v>0.76</v>
       </c>
       <c r="K9" s="6"/>
@@ -1135,31 +1145,31 @@
       <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="8">
-        <v>781999436</v>
-      </c>
-      <c r="C10" s="9">
+      <c r="B10" s="7">
+        <v>78.199943599999997</v>
+      </c>
+      <c r="C10" s="8">
         <v>64303.5</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>3301.5</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="9">
         <v>116811.75</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="9">
         <v>13534.5</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <v>96.45</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <v>83.54</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="10">
         <v>8.64</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="10">
         <v>3.56</v>
       </c>
       <c r="K10" s="6"/>
@@ -1182,31 +1192,31 @@
       <c r="A11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="8">
-        <v>719564162</v>
-      </c>
-      <c r="C11" s="9">
+      <c r="B11" s="7">
+        <v>71.956416200000007</v>
+      </c>
+      <c r="C11" s="8">
         <v>688.29</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>23.73</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="9">
         <v>381729.88</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="9">
         <v>13772.5</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <v>90.96</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <v>94.6</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="10">
         <v>5.61</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="10">
         <v>3.99</v>
       </c>
       <c r="K11" s="6"/>
@@ -1229,31 +1239,31 @@
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="8">
-        <v>715183137</v>
-      </c>
-      <c r="C12" s="9">
+      <c r="B12" s="7">
+        <v>71.518313699999993</v>
+      </c>
+      <c r="C12" s="8">
         <v>1487.45</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>0</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <v>3926153.3</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <v>13166.5</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <v>93.98</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="8">
         <v>99.98</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="10">
         <v>8.01</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="10">
         <v>2.48</v>
       </c>
       <c r="K12" s="6"/>
@@ -1276,31 +1286,31 @@
       <c r="A13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="8">
-        <v>749458173</v>
-      </c>
-      <c r="C13" s="9">
+      <c r="B13" s="7">
+        <v>74.945817300000002</v>
+      </c>
+      <c r="C13" s="8">
         <v>10226653.75</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>794815.39</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="9">
         <v>3038667.95</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="9">
         <v>13067</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="9">
         <v>76.2</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="8">
         <v>95.84</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="10">
         <v>9.0299999999999994</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="10">
         <v>1.59</v>
       </c>
       <c r="K13" s="6"/>
@@ -1323,31 +1333,31 @@
       <c r="A14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="8">
-        <v>737328521</v>
-      </c>
-      <c r="C14" s="9">
+      <c r="B14" s="7">
+        <v>73.732852100000002</v>
+      </c>
+      <c r="C14" s="8">
         <v>9304062.8399999999</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>2750971.45</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>1943187.66</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="9">
         <v>13112.5</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <v>87.51</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="8">
         <v>95.73</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="10">
         <v>8.86</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="10">
         <v>1.77</v>
       </c>
       <c r="K14" s="6"/>
@@ -1370,31 +1380,31 @@
       <c r="A15" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="8">
-        <v>774391712</v>
-      </c>
-      <c r="C15" s="9">
+      <c r="B15" s="7">
+        <v>77.439171200000004</v>
+      </c>
+      <c r="C15" s="8">
         <v>547510.1</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <v>210518.17</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="9">
         <v>208133.8</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="9">
         <v>13024</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="9">
         <v>96.94</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <v>97.33</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="10">
         <v>8.1199999999999992</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="10">
         <v>2.6</v>
       </c>
       <c r="K15" s="6"/>
@@ -1417,31 +1427,31 @@
       <c r="A16" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="8">
-        <v>726692502</v>
-      </c>
-      <c r="C16" s="9">
+      <c r="B16" s="7">
+        <v>72.669250199999993</v>
+      </c>
+      <c r="C16" s="8">
         <v>10438360.58</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="9">
         <v>4587515.95</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="9">
         <v>3403166.85</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="9">
         <v>12719</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="9">
         <v>88.26</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="8">
         <v>97.3</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="10">
         <v>7.15</v>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="10">
         <v>1.53</v>
       </c>
       <c r="K16" s="6"/>
@@ -1460,35 +1470,35 @@
       <c r="X16" s="6"/>
       <c r="Y16" s="6"/>
     </row>
-    <row r="17" spans="1:25" ht="40.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="17" spans="1:25" ht="21" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A17" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="8">
-        <v>77784635</v>
-      </c>
-      <c r="C17" s="9">
+      <c r="B17" s="7">
+        <v>77.784634999999994</v>
+      </c>
+      <c r="C17" s="8">
         <v>1774016.87</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>14645.85</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <v>936203.98</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <v>12816</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <v>90.71</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="8">
         <v>96.03</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="10">
         <v>7.99</v>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="10">
         <v>1.8</v>
       </c>
       <c r="K17" s="6"/>
@@ -1507,35 +1517,35 @@
       <c r="X17" s="6"/>
       <c r="Y17" s="6"/>
     </row>
-    <row r="18" spans="1:25" ht="40.5" thickBot="1" x14ac:dyDescent="0.9">
+    <row r="18" spans="1:25" ht="21" thickBot="1" x14ac:dyDescent="0.9">
       <c r="A18" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="8">
-        <v>798890757</v>
-      </c>
-      <c r="C18" s="9">
+      <c r="B18" s="7">
+        <v>79.889075700000006</v>
+      </c>
+      <c r="C18" s="8">
         <v>587866.28</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="9">
         <v>38139.379999999997</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="9">
         <v>324148.94</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="9">
         <v>14143.5</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="9">
         <v>98.2</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="8">
         <v>98.75</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="10">
         <v>6.33</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="10">
         <v>1.4</v>
       </c>
       <c r="K18" s="6"/>
@@ -1558,31 +1568,31 @@
       <c r="A19" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="8">
-        <v>746963282</v>
-      </c>
-      <c r="C19" s="9">
+      <c r="B19" s="7">
+        <v>74.696328199999996</v>
+      </c>
+      <c r="C19" s="8">
         <v>1708618.85</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>1175151.8</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="9">
         <v>192951.54</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="9">
         <v>13404.5</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="9">
         <v>88.29</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="8">
         <v>96.29</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="10">
         <v>4.7699999999999996</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="10">
         <v>1</v>
       </c>
       <c r="K19" s="6"/>
@@ -1605,31 +1615,31 @@
       <c r="A20" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="8">
-        <v>582444433</v>
-      </c>
-      <c r="C20" s="9">
+      <c r="B20" s="7">
+        <v>58.2444433</v>
+      </c>
+      <c r="C20" s="8">
         <v>968324.36</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>305335.44</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="9">
         <v>148373.38</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="9">
         <v>13703.5</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="9">
         <v>80.8</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="8">
         <v>89.86</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="10">
         <v>3.77</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="10">
         <v>2.81</v>
       </c>
       <c r="K20" s="6"/>
@@ -1652,31 +1662,31 @@
       <c r="A21" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="8">
-        <v>715160036</v>
-      </c>
-      <c r="C21" s="9">
+      <c r="B21" s="7">
+        <v>71.516003600000005</v>
+      </c>
+      <c r="C21" s="8">
         <v>757829.16</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>181841.98</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="9">
         <v>328569.51</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="9">
         <v>14620.5</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="9">
         <v>88.37</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="8">
         <v>84.32</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="10">
         <v>9.83</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="10">
         <v>0.1</v>
       </c>
       <c r="K21" s="6"/>
@@ -1699,31 +1709,31 @@
       <c r="A22" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="8">
-        <v>73619316</v>
-      </c>
-      <c r="C22" s="9">
+      <c r="B22" s="7">
+        <v>73.619315999999998</v>
+      </c>
+      <c r="C22" s="8">
         <v>333428.63</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <v>43874.17</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="9">
         <v>241055.7</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="9">
         <v>14587.5</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="9">
         <v>83.14</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="8">
         <v>80.58</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="10">
         <v>9.6999999999999993</v>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="10">
         <v>0.09</v>
       </c>
       <c r="K22" s="6"/>
@@ -1746,31 +1756,31 @@
       <c r="A23" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="8">
-        <v>81984257</v>
-      </c>
-      <c r="C23" s="9">
+      <c r="B23" s="7">
+        <v>81.984256999999999</v>
+      </c>
+      <c r="C23" s="8">
         <v>1179338.3700000001</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="9">
         <v>159092.75</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="9">
         <v>305126.93</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="9">
         <v>13065</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="9">
         <v>86.8</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="8">
         <v>78.27</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="10">
         <v>8.36</v>
       </c>
-      <c r="J23" s="11">
+      <c r="J23" s="10">
         <v>0.09</v>
       </c>
       <c r="K23" s="6"/>
@@ -1793,31 +1803,31 @@
       <c r="A24" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="8">
-        <v>808175852</v>
-      </c>
-      <c r="C24" s="9">
+      <c r="B24" s="7">
+        <v>80.817585199999996</v>
+      </c>
+      <c r="C24" s="8">
         <v>270866.92</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="9">
         <v>10292.42</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="9">
         <v>889072.55</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="9">
         <v>15478.5</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="9">
         <v>92.57</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="8">
         <v>88.45</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="10">
         <v>8.48</v>
       </c>
-      <c r="J24" s="11">
+      <c r="J24" s="10">
         <v>0.1</v>
       </c>
       <c r="K24" s="6"/>
@@ -1840,31 +1850,31 @@
       <c r="A25" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="8">
-        <v>725567565</v>
-      </c>
-      <c r="C25" s="9">
+      <c r="B25" s="7">
+        <v>72.556756500000006</v>
+      </c>
+      <c r="C25" s="8">
         <v>38038.080000000002</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="9">
         <v>5060.75</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="9">
         <v>156025.74</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="9">
         <v>14761</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="9">
         <v>86</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="8">
         <v>91.59</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="10">
         <v>10.06</v>
       </c>
-      <c r="J25" s="11">
+      <c r="J25" s="10">
         <v>0.1</v>
       </c>
       <c r="K25" s="6"/>
@@ -1887,31 +1897,31 @@
       <c r="A26" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="8">
-        <v>724902207</v>
-      </c>
-      <c r="C26" s="9">
+      <c r="B26" s="7">
+        <v>72.490220699999995</v>
+      </c>
+      <c r="C26" s="8">
         <v>265111.82</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="9">
         <v>108365.39</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="9">
         <v>204747.14</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="9">
         <v>13673</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="9">
         <v>87.72</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="8">
         <v>94.86</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="10">
         <v>7.46</v>
       </c>
-      <c r="J26" s="11">
+      <c r="J26" s="10">
         <v>2.87</v>
       </c>
       <c r="K26" s="6"/>
@@ -1934,31 +1944,31 @@
       <c r="A27" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="8">
-        <v>703981453</v>
-      </c>
-      <c r="C27" s="9">
+      <c r="B27" s="7">
+        <v>70.398145299999996</v>
+      </c>
+      <c r="C27" s="8">
         <v>920086.08</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="9">
         <v>82889.759999999995</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="9">
         <v>415477.22</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="9">
         <v>13430</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="9">
         <v>79.62</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="8">
         <v>87.55</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="10">
         <v>4.08</v>
       </c>
-      <c r="J27" s="11">
+      <c r="J27" s="10">
         <v>2.2799999999999998</v>
       </c>
       <c r="K27" s="6"/>
@@ -1981,31 +1991,31 @@
       <c r="A28" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="8">
-        <v>742975086</v>
-      </c>
-      <c r="C28" s="9">
+      <c r="B28" s="7">
+        <v>74.2975086</v>
+      </c>
+      <c r="C28" s="8">
         <v>5466592.3600000003</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="9">
         <v>1295645.81</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="9">
         <v>753077.16</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="9">
         <v>12841</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="9">
         <v>94.19</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="8">
         <v>93.25</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="10">
         <v>6.2</v>
       </c>
-      <c r="J28" s="11">
+      <c r="J28" s="10">
         <v>0.76</v>
       </c>
       <c r="K28" s="6"/>
@@ -2028,31 +2038,31 @@
       <c r="A29" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="8">
-        <v>675554548</v>
-      </c>
-      <c r="C29" s="9">
+      <c r="B29" s="7">
+        <v>67.555454800000007</v>
+      </c>
+      <c r="C29" s="8">
         <v>680820.2</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="9">
         <v>54804.41</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="9">
         <v>204333.57</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="9">
         <v>13150.5</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="9">
         <v>91.96</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="8">
         <v>94.91</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="10">
         <v>5.0599999999999996</v>
       </c>
-      <c r="J29" s="11">
+      <c r="J29" s="10">
         <v>0.13</v>
       </c>
       <c r="K29" s="6"/>
@@ -2075,31 +2085,31 @@
       <c r="A30" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="8">
-        <v>697453579</v>
-      </c>
-      <c r="C30" s="9">
+      <c r="B30" s="7">
+        <v>69.745357900000002</v>
+      </c>
+      <c r="C30" s="8">
         <v>281171.26</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="9">
         <v>653286.38</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="9">
         <v>58977.51</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="9">
         <v>13329.5</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="9">
         <v>84.7</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="8">
         <v>95.95</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="10">
         <v>7</v>
       </c>
-      <c r="J30" s="11">
+      <c r="J30" s="10">
         <v>2.4500000000000002</v>
       </c>
       <c r="K30" s="6"/>
@@ -2122,31 +2132,31 @@
       <c r="A31" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="8">
-        <v>670763149</v>
-      </c>
-      <c r="C31" s="9">
+      <c r="B31" s="7">
+        <v>67.0763149</v>
+      </c>
+      <c r="C31" s="8">
         <v>386084.41</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <v>23810.799999999999</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="9">
         <v>71162.44</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="9">
         <v>13173.5</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="9">
         <v>85.98</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="8">
         <v>83</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="10">
         <v>5.0199999999999996</v>
       </c>
-      <c r="J31" s="11">
+      <c r="J31" s="10">
         <v>0.26</v>
       </c>
       <c r="K31" s="6"/>
@@ -2169,31 +2179,31 @@
       <c r="A32" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="8">
-        <v>571792945</v>
-      </c>
-      <c r="C32" s="9">
+      <c r="B32" s="7">
+        <v>57.179294499999997</v>
+      </c>
+      <c r="C32" s="8">
         <v>103818.57</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="9">
         <v>6930.9</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="9">
         <v>66313.119999999995</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="9">
         <v>14401</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="9">
         <v>83.09</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="8">
         <v>92.83</v>
       </c>
-      <c r="I32" s="11">
+      <c r="I32" s="10">
         <v>10.77</v>
       </c>
-      <c r="J32" s="11">
+      <c r="J32" s="10">
         <v>1.79</v>
       </c>
       <c r="K32" s="6"/>
@@ -2216,31 +2226,31 @@
       <c r="A33" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="8">
-        <v>582717474</v>
-      </c>
-      <c r="C33" s="9">
+      <c r="B33" s="7">
+        <v>58.271747400000002</v>
+      </c>
+      <c r="C33" s="8">
         <v>22641.62</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="9">
         <v>4133.96</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="9">
         <v>133620.32</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="9">
         <v>15666</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="9">
         <v>84.12</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="8">
         <v>90.01</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33" s="10">
         <v>8.36</v>
       </c>
-      <c r="J33" s="11">
+      <c r="J33" s="10">
         <v>2.4300000000000002</v>
       </c>
       <c r="K33" s="6"/>
@@ -2263,31 +2273,31 @@
       <c r="A34" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="8">
-        <v>574540166</v>
-      </c>
-      <c r="C34" s="9">
+      <c r="B34" s="7">
+        <v>57.454016600000003</v>
+      </c>
+      <c r="C34" s="8">
         <v>13365.79</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="9">
         <v>1304.17</v>
       </c>
-      <c r="E34" s="10">
+      <c r="E34" s="9">
         <v>90513.18</v>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="9">
         <v>15188.5</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="9">
         <v>76.709999999999994</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="8">
         <v>87.7</v>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="10">
         <v>11.72</v>
       </c>
-      <c r="J34" s="11">
+      <c r="J34" s="10">
         <v>0.21</v>
       </c>
       <c r="K34" s="6"/>
@@ -2310,31 +2320,31 @@
       <c r="A35" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="8">
-        <v>586075685</v>
-      </c>
-      <c r="C35" s="9">
+      <c r="B35" s="7">
+        <v>58.607568499999999</v>
+      </c>
+      <c r="C35" s="8">
         <v>830.38</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="9">
         <v>2734.93</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="9">
         <v>81807.570000000007</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="9">
         <v>16471.5</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="9">
         <v>78.55</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="8">
         <v>82.95</v>
       </c>
-      <c r="I35" s="11">
+      <c r="I35" s="10">
         <v>7.9</v>
       </c>
-      <c r="J35" s="11">
+      <c r="J35" s="10">
         <v>0.64</v>
       </c>
       <c r="K35" s="6"/>
@@ -2357,31 +2367,31 @@
       <c r="A36" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="8">
-        <v>539644654</v>
-      </c>
-      <c r="C36" s="9">
+      <c r="B36" s="7">
+        <v>53.964465400000002</v>
+      </c>
+      <c r="C36" s="8">
         <v>1859.06</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="9">
         <v>2414.5500000000002</v>
       </c>
-      <c r="E36" s="10">
+      <c r="E36" s="9">
         <v>35687.86</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F36" s="12">
         <v>0</v>
       </c>
-      <c r="G36" s="10">
+      <c r="G36" s="9">
         <v>65.06</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="8">
         <v>71.28</v>
       </c>
-      <c r="I36" s="11">
+      <c r="I36" s="10">
         <v>11.97</v>
       </c>
-      <c r="J36" s="11">
+      <c r="J36" s="10">
         <v>0.06</v>
       </c>
       <c r="K36" s="6"/>
@@ -2404,31 +2414,31 @@
       <c r="A37" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="8">
-        <v>416092347</v>
-      </c>
-      <c r="C37" s="9">
+      <c r="B37" s="7">
+        <v>41.609234700000002</v>
+      </c>
+      <c r="C37" s="8">
         <v>362542.11</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37" s="9">
         <v>2909.57</v>
       </c>
-      <c r="E37" s="10">
+      <c r="E37" s="9">
         <v>160519.15</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="9">
         <v>15381.5</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G37" s="9">
         <v>39.729999999999997</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="8">
         <v>83.21</v>
       </c>
-      <c r="I37" s="11">
+      <c r="I37" s="10">
         <v>17.96</v>
       </c>
-      <c r="J37" s="11">
+      <c r="J37" s="10">
         <v>0.34</v>
       </c>
       <c r="K37" s="6"/>
@@ -2451,31 +2461,31 @@
       <c r="A38" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="8">
-        <v>31962763</v>
-      </c>
-      <c r="C38" s="9">
+      <c r="B38" s="7">
+        <v>31.962762999999999</v>
+      </c>
+      <c r="C38" s="8">
         <v>3805.44</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="9">
         <v>4391.79</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="9">
         <v>28377.77</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="9">
         <v>24583.5</v>
       </c>
-      <c r="G38" s="10">
+      <c r="G38" s="9">
         <v>16.34</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="8">
         <v>32.89</v>
       </c>
-      <c r="I38" s="11">
+      <c r="I38" s="10">
         <v>8.85</v>
       </c>
-      <c r="J38" s="11">
+      <c r="J38" s="10">
         <v>1.25</v>
       </c>
       <c r="K38" s="6"/>
@@ -2498,31 +2508,31 @@
       <c r="A39" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="8">
-        <v>571545916</v>
-      </c>
-      <c r="C39" s="9">
+      <c r="B39" s="7">
+        <v>57.154591600000003</v>
+      </c>
+      <c r="C39" s="8">
         <v>89.42</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D39" s="9">
         <v>231.29</v>
       </c>
-      <c r="E39" s="10">
+      <c r="E39" s="9">
         <v>39219.64</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="9">
         <v>15561</v>
       </c>
-      <c r="G39" s="10">
+      <c r="G39" s="9">
         <v>79.56</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="8">
         <v>80.64</v>
       </c>
-      <c r="I39" s="11">
+      <c r="I39" s="10">
         <v>11.19</v>
       </c>
-      <c r="J39" s="11">
+      <c r="J39" s="10">
         <v>1.17</v>
       </c>
       <c r="K39" s="6"/>
